--- a/tests/DotnetPoi.Interop.Tests/fixtures/xml-parity/_workbooks/cell-types.xlsx
+++ b/tests/DotnetPoi.Interop.Tests/fixtures/xml-parity/_workbooks/cell-types.xlsx
@@ -76,7 +76,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="n" s="1">
-        <v>25569.375</v>
+        <v>25569.0</v>
       </c>
       <c r="E1" s="0">
         <f>SUM(1,2,3)</f>
